--- a/预测水位/OutputData/SK09.xlsx
+++ b/预测水位/OutputData/SK09.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1046,10 +1046,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B2161"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:B2317"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="24.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="24.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -18257,99 +18257,1345 @@
       </c>
     </row>
     <row r="2150" spans="1:2">
-      <c r="A2150" s="7">
+      <c r="A2150" s="5">
         <v>45837</v>
       </c>
-      <c r="B2150" s="8">
+      <c r="B2150" s="6">
         <v>919.279</v>
       </c>
     </row>
     <row r="2151" spans="1:2">
-      <c r="A2151" s="7">
+      <c r="A2151" s="5">
         <v>45837.0833333333</v>
       </c>
-      <c r="B2151" s="8">
+      <c r="B2151" s="6">
         <v>919.44</v>
       </c>
     </row>
     <row r="2152" spans="1:2">
-      <c r="A2152" s="7">
+      <c r="A2152" s="5">
         <v>45837.1666666667</v>
       </c>
-      <c r="B2152" s="8">
+      <c r="B2152" s="6">
         <v>919.579</v>
       </c>
     </row>
     <row r="2153" spans="1:2">
-      <c r="A2153" s="7">
+      <c r="A2153" s="5">
         <v>45837.25</v>
       </c>
-      <c r="B2153" s="8">
+      <c r="B2153" s="6">
         <v>919.707</v>
       </c>
     </row>
     <row r="2154" spans="1:2">
-      <c r="A2154" s="7">
+      <c r="A2154" s="5">
         <v>45837.3333333333</v>
       </c>
-      <c r="B2154" s="8">
+      <c r="B2154" s="6">
         <v>919.812</v>
       </c>
     </row>
     <row r="2155" spans="1:2">
-      <c r="A2155" s="7">
+      <c r="A2155" s="5">
         <v>45837.4166666667</v>
       </c>
-      <c r="B2155" s="8">
+      <c r="B2155" s="6">
         <v>919.907</v>
       </c>
     </row>
     <row r="2156" spans="1:2">
-      <c r="A2156" s="7">
+      <c r="A2156" s="5">
         <v>45837.5</v>
       </c>
-      <c r="B2156" s="8">
+      <c r="B2156" s="6">
         <v>919.996</v>
       </c>
     </row>
     <row r="2157" spans="1:2">
-      <c r="A2157" s="7">
+      <c r="A2157" s="5">
         <v>45837.5833333333</v>
       </c>
-      <c r="B2157" s="8">
+      <c r="B2157" s="6">
         <v>920.077</v>
       </c>
     </row>
     <row r="2158" spans="1:2">
-      <c r="A2158" s="7">
+      <c r="A2158" s="5">
         <v>45837.6666666667</v>
       </c>
-      <c r="B2158" s="8">
+      <c r="B2158" s="6">
         <v>920.154</v>
       </c>
     </row>
     <row r="2159" spans="1:2">
-      <c r="A2159" s="7">
+      <c r="A2159" s="5">
         <v>45837.75</v>
       </c>
-      <c r="B2159" s="8">
+      <c r="B2159" s="6">
         <v>920.227</v>
       </c>
     </row>
     <row r="2160" spans="1:2">
-      <c r="A2160" s="7">
+      <c r="A2160" s="5">
         <v>45837.8333333333</v>
       </c>
-      <c r="B2160" s="8">
+      <c r="B2160" s="6">
         <v>920.289</v>
       </c>
     </row>
     <row r="2161" spans="1:2">
-      <c r="A2161" s="7">
+      <c r="A2161" s="5">
         <v>45837.9166666667</v>
       </c>
-      <c r="B2161" s="8">
+      <c r="B2161" s="6">
         <v>920.345</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:2">
+      <c r="A2162" s="5">
+        <v>45838</v>
+      </c>
+      <c r="B2162" s="6">
+        <v>920.395</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:2">
+      <c r="A2163" s="5">
+        <v>45838.0833333333</v>
+      </c>
+      <c r="B2163" s="6"/>
+    </row>
+    <row r="2164" spans="1:2">
+      <c r="A2164" s="5">
+        <v>45838.1666666667</v>
+      </c>
+      <c r="B2164" s="6">
+        <v>920.476</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:2">
+      <c r="A2165" s="5">
+        <v>45838.25</v>
+      </c>
+      <c r="B2165" s="6">
+        <v>920.502</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:2">
+      <c r="A2166" s="5">
+        <v>45838.3333333333</v>
+      </c>
+      <c r="B2166" s="6">
+        <v>920.527</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:2">
+      <c r="A2167" s="5">
+        <v>45838.4166666667</v>
+      </c>
+      <c r="B2167" s="6">
+        <v>920.548</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:2">
+      <c r="A2168" s="5">
+        <v>45838.5</v>
+      </c>
+      <c r="B2168" s="6">
+        <v>920.564</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:2">
+      <c r="A2169" s="5">
+        <v>45838.5833333333</v>
+      </c>
+      <c r="B2169" s="6">
+        <v>920.58</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:2">
+      <c r="A2170" s="5">
+        <v>45838.6666666667</v>
+      </c>
+      <c r="B2170" s="6">
+        <v>920.593</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:2">
+      <c r="A2171" s="5">
+        <v>45838.75</v>
+      </c>
+      <c r="B2171" s="6">
+        <v>920.615</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:2">
+      <c r="A2172" s="5">
+        <v>45838.8333333333</v>
+      </c>
+      <c r="B2172" s="6">
+        <v>920.633</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:2">
+      <c r="A2173" s="5">
+        <v>45838.9166666667</v>
+      </c>
+      <c r="B2173" s="6">
+        <v>920.646</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:2">
+      <c r="A2174" s="5">
+        <v>45839</v>
+      </c>
+      <c r="B2174" s="6">
+        <v>920.651</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:2">
+      <c r="A2175" s="5">
+        <v>45839.0833333333</v>
+      </c>
+      <c r="B2175" s="6">
+        <v>920.648</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:2">
+      <c r="A2176" s="5">
+        <v>45839.1666666667</v>
+      </c>
+      <c r="B2176" s="6">
+        <v>920.633</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:2">
+      <c r="A2177" s="5">
+        <v>45839.25</v>
+      </c>
+      <c r="B2177" s="6">
+        <v>920.621</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:2">
+      <c r="A2178" s="5">
+        <v>45839.3333333333</v>
+      </c>
+      <c r="B2178" s="6">
+        <v>920.611</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:2">
+      <c r="A2179" s="5">
+        <v>45839.4166666667</v>
+      </c>
+      <c r="B2179" s="6">
+        <v>920.601</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:2">
+      <c r="A2180" s="5">
+        <v>45839.5</v>
+      </c>
+      <c r="B2180" s="6">
+        <v>920.582</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:2">
+      <c r="A2181" s="5">
+        <v>45839.5833333333</v>
+      </c>
+      <c r="B2181" s="6">
+        <v>920.556</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:2">
+      <c r="A2182" s="5">
+        <v>45839.6666666667</v>
+      </c>
+      <c r="B2182" s="6">
+        <v>920.533</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:2">
+      <c r="A2183" s="5">
+        <v>45839.75</v>
+      </c>
+      <c r="B2183" s="6">
+        <v>920.517</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:2">
+      <c r="A2184" s="5">
+        <v>45839.8333333333</v>
+      </c>
+      <c r="B2184" s="6">
+        <v>920.507</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:2">
+      <c r="A2185" s="5">
+        <v>45839.9166666667</v>
+      </c>
+      <c r="B2185" s="6">
+        <v>920.489</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:2">
+      <c r="A2186" s="5">
+        <v>45840</v>
+      </c>
+      <c r="B2186" s="6">
+        <v>920.467</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:2">
+      <c r="A2187" s="5">
+        <v>45840.0833333333</v>
+      </c>
+      <c r="B2187" s="6">
+        <v>920.435</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:2">
+      <c r="A2188" s="5">
+        <v>45840.1666666667</v>
+      </c>
+      <c r="B2188" s="6">
+        <v>920.387</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:2">
+      <c r="A2189" s="5">
+        <v>45840.25</v>
+      </c>
+      <c r="B2189" s="6">
+        <v>920.349</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:2">
+      <c r="A2190" s="5">
+        <v>45840.3333333333</v>
+      </c>
+      <c r="B2190" s="6">
+        <v>920.309</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:2">
+      <c r="A2191" s="5">
+        <v>45840.4166666667</v>
+      </c>
+      <c r="B2191" s="6">
+        <v>920.272</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:2">
+      <c r="A2192" s="5">
+        <v>45840.5</v>
+      </c>
+      <c r="B2192" s="6">
+        <v>920.227</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:2">
+      <c r="A2193" s="5">
+        <v>45840.5833333333</v>
+      </c>
+      <c r="B2193" s="6">
+        <v>920.185</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:2">
+      <c r="A2194" s="5">
+        <v>45840.6666666667</v>
+      </c>
+      <c r="B2194" s="6">
+        <v>920.138</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:2">
+      <c r="A2195" s="5">
+        <v>45840.75</v>
+      </c>
+      <c r="B2195" s="6">
+        <v>920.106</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:2">
+      <c r="A2196" s="5">
+        <v>45840.8333333333</v>
+      </c>
+      <c r="B2196" s="6">
+        <v>920.08</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:2">
+      <c r="A2197" s="5">
+        <v>45840.9166666667</v>
+      </c>
+      <c r="B2197" s="6">
+        <v>920.052</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:2">
+      <c r="A2198" s="5">
+        <v>45841</v>
+      </c>
+      <c r="B2198" s="6">
+        <v>920.024</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:2">
+      <c r="A2199" s="5">
+        <v>45841.0833333333</v>
+      </c>
+      <c r="B2199" s="6">
+        <v>919.977</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:2">
+      <c r="A2200" s="5">
+        <v>45841.1666666667</v>
+      </c>
+      <c r="B2200" s="6">
+        <v>919.919</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:2">
+      <c r="A2201" s="5">
+        <v>45841.25</v>
+      </c>
+      <c r="B2201" s="6">
+        <v>919.869</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:2">
+      <c r="A2202" s="5">
+        <v>45841.3333333333</v>
+      </c>
+      <c r="B2202" s="6">
+        <v>919.823</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:2">
+      <c r="A2203" s="5">
+        <v>45841.4166666667</v>
+      </c>
+      <c r="B2203" s="6">
+        <v>919.789</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:2">
+      <c r="A2204" s="5">
+        <v>45841.5</v>
+      </c>
+      <c r="B2204" s="6">
+        <v>919.744</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:2">
+      <c r="A2205" s="5">
+        <v>45841.5833333333</v>
+      </c>
+      <c r="B2205" s="6">
+        <v>919.7</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:2">
+      <c r="A2206" s="5">
+        <v>45841.6666666667</v>
+      </c>
+      <c r="B2206" s="6">
+        <v>919.647</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:2">
+      <c r="A2207" s="5">
+        <v>45841.75</v>
+      </c>
+      <c r="B2207" s="6">
+        <v>919.611</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:2">
+      <c r="A2208" s="5">
+        <v>45841.8333333333</v>
+      </c>
+      <c r="B2208" s="6">
+        <v>919.584</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:2">
+      <c r="A2209" s="5">
+        <v>45841.9166666667</v>
+      </c>
+      <c r="B2209" s="6">
+        <v>919.551</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:2">
+      <c r="A2210" s="5">
+        <v>45842</v>
+      </c>
+      <c r="B2210" s="6">
+        <v>919.514</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:2">
+      <c r="A2211" s="5">
+        <v>45842.0833333333</v>
+      </c>
+      <c r="B2211" s="6">
+        <v>919.472</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:2">
+      <c r="A2212" s="5">
+        <v>45842.1666666667</v>
+      </c>
+      <c r="B2212" s="6">
+        <v>919.416</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:2">
+      <c r="A2213" s="5">
+        <v>45842.25</v>
+      </c>
+      <c r="B2213" s="6">
+        <v>919.364</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:2">
+      <c r="A2214" s="5">
+        <v>45842.3333333333</v>
+      </c>
+      <c r="B2214" s="6">
+        <v>919.322</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:2">
+      <c r="A2215" s="5">
+        <v>45842.4166666667</v>
+      </c>
+      <c r="B2215" s="6">
+        <v>919.287</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:2">
+      <c r="A2216" s="5">
+        <v>45842.5</v>
+      </c>
+      <c r="B2216" s="6">
+        <v>919.246</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:2">
+      <c r="A2217" s="5">
+        <v>45842.5833333333</v>
+      </c>
+      <c r="B2217" s="6">
+        <v>919.195</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:2">
+      <c r="A2218" s="5">
+        <v>45842.6666666667</v>
+      </c>
+      <c r="B2218" s="6">
+        <v>919.142</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:2">
+      <c r="A2219" s="5">
+        <v>45842.75</v>
+      </c>
+      <c r="B2219" s="6">
+        <v>919.096</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:2">
+      <c r="A2220" s="5">
+        <v>45842.8333333333</v>
+      </c>
+      <c r="B2220" s="6">
+        <v>919.067</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:2">
+      <c r="A2221" s="5">
+        <v>45842.9166666667</v>
+      </c>
+      <c r="B2221" s="6">
+        <v>919.048</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:2">
+      <c r="A2222" s="5">
+        <v>45843</v>
+      </c>
+      <c r="B2222" s="6">
+        <v>919.02</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:2">
+      <c r="A2223" s="5">
+        <v>45843.0833333333</v>
+      </c>
+      <c r="B2223" s="6">
+        <v>918.954</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:2">
+      <c r="A2224" s="5">
+        <v>45843.1666666667</v>
+      </c>
+      <c r="B2224" s="6">
+        <v>918.9</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:2">
+      <c r="A2225" s="5">
+        <v>45843.25</v>
+      </c>
+      <c r="B2225" s="6">
+        <v>918.854</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:2">
+      <c r="A2226" s="5">
+        <v>45843.3333333333</v>
+      </c>
+      <c r="B2226" s="6">
+        <v>918.831</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:2">
+      <c r="A2227" s="5">
+        <v>45843.4166666667</v>
+      </c>
+      <c r="B2227" s="6">
+        <v>918.831</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:2">
+      <c r="A2228" s="5">
+        <v>45843.5</v>
+      </c>
+      <c r="B2228" s="6">
+        <v>918.819</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:2">
+      <c r="A2229" s="5">
+        <v>45843.5833333333</v>
+      </c>
+      <c r="B2229" s="6">
+        <v>918.796</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:2">
+      <c r="A2230" s="5">
+        <v>45843.6666666667</v>
+      </c>
+      <c r="B2230" s="6">
+        <v>918.76</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:2">
+      <c r="A2231" s="5">
+        <v>45843.75</v>
+      </c>
+      <c r="B2231" s="6">
+        <v>918.731</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:2">
+      <c r="A2232" s="5">
+        <v>45843.8333333333</v>
+      </c>
+      <c r="B2232" s="6">
+        <v>918.715</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:2">
+      <c r="A2233" s="5">
+        <v>45843.9166666667</v>
+      </c>
+      <c r="B2233" s="6">
+        <v>918.707</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:2">
+      <c r="A2234" s="5">
+        <v>45844</v>
+      </c>
+      <c r="B2234" s="6">
+        <v>918.694</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:2">
+      <c r="A2235" s="5">
+        <v>45844.0833333333</v>
+      </c>
+      <c r="B2235" s="6">
+        <v>918.652</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:2">
+      <c r="A2236" s="5">
+        <v>45844.1666666667</v>
+      </c>
+      <c r="B2236" s="6">
+        <v>918.596</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:2">
+      <c r="A2237" s="5">
+        <v>45844.25</v>
+      </c>
+      <c r="B2237" s="6">
+        <v>918.549</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:2">
+      <c r="A2238" s="5">
+        <v>45844.3333333333</v>
+      </c>
+      <c r="B2238" s="6">
+        <v>918.515</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:2">
+      <c r="A2239" s="5">
+        <v>45844.4166666667</v>
+      </c>
+      <c r="B2239" s="6">
+        <v>918.488</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:2">
+      <c r="A2240" s="5">
+        <v>45844.5</v>
+      </c>
+      <c r="B2240" s="6">
+        <v>918.46</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:2">
+      <c r="A2241" s="5">
+        <v>45844.5833333333</v>
+      </c>
+      <c r="B2241" s="6">
+        <v>918.417</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:2">
+      <c r="A2242" s="5">
+        <v>45844.6666666667</v>
+      </c>
+      <c r="B2242" s="6">
+        <v>918.367</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:2">
+      <c r="A2243" s="5">
+        <v>45844.75</v>
+      </c>
+      <c r="B2243" s="6">
+        <v>918.32</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:2">
+      <c r="A2244" s="5">
+        <v>45844.8333333333</v>
+      </c>
+      <c r="B2244" s="6">
+        <v>918.29</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:2">
+      <c r="A2245" s="5">
+        <v>45844.9166666667</v>
+      </c>
+      <c r="B2245" s="6">
+        <v>918.272</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:2">
+      <c r="A2246" s="5">
+        <v>45845</v>
+      </c>
+      <c r="B2246" s="6">
+        <v>918.249</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:2">
+      <c r="A2247" s="5">
+        <v>45845.0833333333</v>
+      </c>
+      <c r="B2247" s="6">
+        <v>918.211</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:2">
+      <c r="A2248" s="5">
+        <v>45845.1666666667</v>
+      </c>
+      <c r="B2248" s="6">
+        <v>918.163</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:2">
+      <c r="A2249" s="5">
+        <v>45845.25</v>
+      </c>
+      <c r="B2249" s="6">
+        <v>918.116</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:2">
+      <c r="A2250" s="5">
+        <v>45845.3333333333</v>
+      </c>
+      <c r="B2250" s="6">
+        <v>918.081</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:2">
+      <c r="A2251" s="5">
+        <v>45845.4166666667</v>
+      </c>
+      <c r="B2251" s="6">
+        <v>918.054</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:2">
+      <c r="A2252" s="5">
+        <v>45845.5</v>
+      </c>
+      <c r="B2252" s="6">
+        <v>922.23</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:2">
+      <c r="A2253" s="5">
+        <v>45845.5833333333</v>
+      </c>
+      <c r="B2253" s="6">
+        <v>922.232</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:2">
+      <c r="A2254" s="5">
+        <v>45845.6666666667</v>
+      </c>
+      <c r="B2254" s="6">
+        <v>922.221</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:2">
+      <c r="A2255" s="5">
+        <v>45845.75</v>
+      </c>
+      <c r="B2255" s="6">
+        <v>922.194</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:2">
+      <c r="A2256" s="5">
+        <v>45845.8333333333</v>
+      </c>
+      <c r="B2256" s="6">
+        <v>922.166</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:2">
+      <c r="A2257" s="5">
+        <v>45845.9166666667</v>
+      </c>
+      <c r="B2257" s="6">
+        <v>922.139</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:2">
+      <c r="A2258" s="5">
+        <v>45846</v>
+      </c>
+      <c r="B2258" s="6">
+        <v>922.12</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:2">
+      <c r="A2259" s="5">
+        <v>45846.0833333333</v>
+      </c>
+      <c r="B2259" s="6">
+        <v>922.111</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:2">
+      <c r="A2260" s="5">
+        <v>45846.1666666667</v>
+      </c>
+      <c r="B2260" s="6">
+        <v>922.096</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:2">
+      <c r="A2261" s="5">
+        <v>45846.25</v>
+      </c>
+      <c r="B2261" s="6">
+        <v>922.078</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:2">
+      <c r="A2262" s="5">
+        <v>45846.3333333333</v>
+      </c>
+      <c r="B2262" s="6">
+        <v>922.054</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:2">
+      <c r="A2263" s="5">
+        <v>45846.4166666667</v>
+      </c>
+      <c r="B2263" s="6">
+        <v>922.023</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:2">
+      <c r="A2264" s="5">
+        <v>45846.5</v>
+      </c>
+      <c r="B2264" s="6">
+        <v>921.997</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:2">
+      <c r="A2265" s="5">
+        <v>45846.5833333333</v>
+      </c>
+      <c r="B2265" s="6">
+        <v>921.966</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:2">
+      <c r="A2266" s="5">
+        <v>45846.6666666667</v>
+      </c>
+      <c r="B2266" s="6">
+        <v>921.937</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:2">
+      <c r="A2267" s="5">
+        <v>45846.75</v>
+      </c>
+      <c r="B2267" s="6">
+        <v>921.906</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:2">
+      <c r="A2268" s="5">
+        <v>45846.8333333333</v>
+      </c>
+      <c r="B2268" s="6">
+        <v>921.871</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:2">
+      <c r="A2269" s="5">
+        <v>45846.9166666667</v>
+      </c>
+      <c r="B2269" s="6">
+        <v>921.838</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:2">
+      <c r="A2270" s="5">
+        <v>45847</v>
+      </c>
+      <c r="B2270" s="6">
+        <v>921.806</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:2">
+      <c r="A2271" s="5">
+        <v>45847.0833333333</v>
+      </c>
+      <c r="B2271" s="6">
+        <v>921.778</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:2">
+      <c r="A2272" s="5">
+        <v>45847.1666666667</v>
+      </c>
+      <c r="B2272" s="6">
+        <v>921.751</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:2">
+      <c r="A2273" s="5">
+        <v>45847.25</v>
+      </c>
+      <c r="B2273" s="6">
+        <v>921.723</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:2">
+      <c r="A2274" s="5">
+        <v>45847.3333333333</v>
+      </c>
+      <c r="B2274" s="6">
+        <v>921.694</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:2">
+      <c r="A2275" s="5">
+        <v>45847.4166666667</v>
+      </c>
+      <c r="B2275" s="6">
+        <v>921.661</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:2">
+      <c r="A2276" s="5">
+        <v>45847.5</v>
+      </c>
+      <c r="B2276" s="6">
+        <v>921.627</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:2">
+      <c r="A2277" s="5">
+        <v>45847.5833333333</v>
+      </c>
+      <c r="B2277" s="6">
+        <v>921.586</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:2">
+      <c r="A2278" s="5">
+        <v>45847.6666666667</v>
+      </c>
+      <c r="B2278" s="6">
+        <v>921.547</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:2">
+      <c r="A2279" s="5">
+        <v>45847.75</v>
+      </c>
+      <c r="B2279" s="6">
+        <v>921.504</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:2">
+      <c r="A2280" s="5">
+        <v>45847.8333333333</v>
+      </c>
+      <c r="B2280" s="6">
+        <v>921.449</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:2">
+      <c r="A2281" s="5">
+        <v>45847.9166666667</v>
+      </c>
+      <c r="B2281" s="6">
+        <v>921.405</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:2">
+      <c r="A2282" s="5">
+        <v>45848</v>
+      </c>
+      <c r="B2282" s="6">
+        <v>921.353</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:2">
+      <c r="A2283" s="5">
+        <v>45848.0833333333</v>
+      </c>
+      <c r="B2283" s="6">
+        <v>921.307</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:2">
+      <c r="A2284" s="5">
+        <v>45848.1666666667</v>
+      </c>
+      <c r="B2284" s="6">
+        <v>921.247</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:2">
+      <c r="A2285" s="5">
+        <v>45848.25</v>
+      </c>
+      <c r="B2285" s="6">
+        <v>921.204</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:2">
+      <c r="A2286" s="5">
+        <v>45848.3333333333</v>
+      </c>
+      <c r="B2286" s="6">
+        <v>921.163</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:2">
+      <c r="A2287" s="5">
+        <v>45848.4166666667</v>
+      </c>
+      <c r="B2287" s="6">
+        <v>921.112</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:2">
+      <c r="A2288" s="5">
+        <v>45848.5</v>
+      </c>
+      <c r="B2288" s="6">
+        <v>921.06</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:2">
+      <c r="A2289" s="5">
+        <v>45848.5833333333</v>
+      </c>
+      <c r="B2289" s="6">
+        <v>921.001</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:2">
+      <c r="A2290" s="5">
+        <v>45848.6666666667</v>
+      </c>
+      <c r="B2290" s="6">
+        <v>920.944</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:2">
+      <c r="A2291" s="5">
+        <v>45848.75</v>
+      </c>
+      <c r="B2291" s="6">
+        <v>920.883</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:2">
+      <c r="A2292" s="5">
+        <v>45848.8333333333</v>
+      </c>
+      <c r="B2292" s="6">
+        <v>920.829</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:2">
+      <c r="A2293" s="5">
+        <v>45848.9166666667</v>
+      </c>
+      <c r="B2293" s="6">
+        <v>920.771</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:2">
+      <c r="A2294" s="5">
+        <v>45849</v>
+      </c>
+      <c r="B2294" s="6">
+        <v>920.709</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:2">
+      <c r="A2295" s="5">
+        <v>45849.0833333333</v>
+      </c>
+      <c r="B2295" s="6">
+        <v>920.653</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:2">
+      <c r="A2296" s="5">
+        <v>45849.1666666667</v>
+      </c>
+      <c r="B2296" s="6">
+        <v>920.602</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:2">
+      <c r="A2297" s="5">
+        <v>45849.25</v>
+      </c>
+      <c r="B2297" s="6">
+        <v>920.568</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:2">
+      <c r="A2298" s="5">
+        <v>45849.3333333333</v>
+      </c>
+      <c r="B2298" s="6">
+        <v>920.538</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:2">
+      <c r="A2299" s="5">
+        <v>45849.4166666667</v>
+      </c>
+      <c r="B2299" s="6">
+        <v>920.506</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:2">
+      <c r="A2300" s="5">
+        <v>45849.5</v>
+      </c>
+      <c r="B2300" s="6">
+        <v>920.456</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:2">
+      <c r="A2301" s="5">
+        <v>45849.5833333333</v>
+      </c>
+      <c r="B2301" s="6">
+        <v>920.394</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:2">
+      <c r="A2302" s="5">
+        <v>45849.6666666667</v>
+      </c>
+      <c r="B2302" s="6">
+        <v>920.343</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:2">
+      <c r="A2303" s="5">
+        <v>45849.75</v>
+      </c>
+      <c r="B2303" s="6">
+        <v>920.315</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:2">
+      <c r="A2304" s="5">
+        <v>45849.8333333333</v>
+      </c>
+      <c r="B2304" s="6">
+        <v>920.276</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:2">
+      <c r="A2305" s="5">
+        <v>45849.9166666667</v>
+      </c>
+      <c r="B2305" s="6">
+        <v>920.243</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:2">
+      <c r="A2306" s="7">
+        <v>45850</v>
+      </c>
+      <c r="B2306" s="8">
+        <v>920.195</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:2">
+      <c r="A2307" s="7">
+        <v>45850.0833333333</v>
+      </c>
+      <c r="B2307" s="8">
+        <v>920.149</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:2">
+      <c r="A2308" s="7">
+        <v>45850.1666666667</v>
+      </c>
+      <c r="B2308" s="8">
+        <v>920.102</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:2">
+      <c r="A2309" s="7">
+        <v>45850.25</v>
+      </c>
+      <c r="B2309" s="8">
+        <v>920.079</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:2">
+      <c r="A2310" s="7">
+        <v>45850.3333333333</v>
+      </c>
+      <c r="B2310" s="8">
+        <v>920.059</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:2">
+      <c r="A2311" s="7">
+        <v>45850.4166666667</v>
+      </c>
+      <c r="B2311" s="8">
+        <v>920.043</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:2">
+      <c r="A2312" s="7">
+        <v>45850.5</v>
+      </c>
+      <c r="B2312" s="8">
+        <v>920.022</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:2">
+      <c r="A2313" s="7">
+        <v>45850.5833333333</v>
+      </c>
+      <c r="B2313" s="8">
+        <v>919.985</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:2">
+      <c r="A2314" s="7">
+        <v>45850.6666666667</v>
+      </c>
+      <c r="B2314" s="8">
+        <v>919.94</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:2">
+      <c r="A2315" s="7">
+        <v>45850.75</v>
+      </c>
+      <c r="B2315" s="8">
+        <v>919.897</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:2">
+      <c r="A2316" s="7">
+        <v>45850.8333333333</v>
+      </c>
+      <c r="B2316" s="8">
+        <v>919.865</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:2">
+      <c r="A2317" s="7">
+        <v>45850.9166666667</v>
+      </c>
+      <c r="B2317" s="8">
+        <v>919.835</v>
       </c>
     </row>
   </sheetData>
